--- a/Resources/SleepyPharmaDrugEffects.xlsx
+++ b/Resources/SleepyPharmaDrugEffects.xlsx
@@ -904,79 +904,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="59">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF69D8FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFE0A9A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF69D8FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor rgb="FFE0A9A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E6A2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
@@ -1192,55 +1120,61 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="B3:Q44" totalsRowShown="0" dataDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="B3:Q44" totalsRowShown="0" dataDxfId="40">
   <autoFilter ref="B3:Q44">
     <filterColumn colId="3"/>
     <filterColumn colId="8"/>
     <filterColumn colId="14"/>
     <filterColumn colId="15"/>
   </autoFilter>
+  <sortState ref="B4:Q44">
+    <sortCondition ref="B3:B44"/>
+  </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" name="Drug" dataDxfId="50"/>
-    <tableColumn id="14" name="Mood Bonus" dataDxfId="49"/>
-    <tableColumn id="13" name="Other Drug Effects" dataDxfId="48"/>
-    <tableColumn id="17" name="Joy" dataDxfId="47"/>
-    <tableColumn id="2" name="Addictiveness" dataDxfId="46"/>
-    <tableColumn id="3" name="Market Value" dataDxfId="45"/>
-    <tableColumn id="4" name="Work to Make" dataDxfId="44"/>
-    <tableColumn id="5" name="Duration (Per Dose)" dataDxfId="43"/>
-    <tableColumn id="18" name="Initial Severity" dataDxfId="42"/>
-    <tableColumn id="6" name="Tolerance Gain (Per Dose)" dataDxfId="41"/>
-    <tableColumn id="7" name="Tolerance Fall Rate" dataDxfId="40"/>
-    <tableColumn id="9" name="Addiction Min Tol" dataDxfId="39"/>
-    <tableColumn id="10" name="OD Chance" dataDxfId="38"/>
-    <tableColumn id="11" name="OD Offset" dataDxfId="37"/>
-    <tableColumn id="19" name="Drug Class" dataDxfId="36"/>
-    <tableColumn id="16" name="Type" dataDxfId="35"/>
+    <tableColumn id="1" name="Drug" dataDxfId="39"/>
+    <tableColumn id="14" name="Mood Bonus" dataDxfId="38"/>
+    <tableColumn id="13" name="Other Drug Effects" dataDxfId="37"/>
+    <tableColumn id="17" name="Joy" dataDxfId="36"/>
+    <tableColumn id="2" name="Addictiveness" dataDxfId="35"/>
+    <tableColumn id="3" name="Market Value" dataDxfId="34"/>
+    <tableColumn id="4" name="Work to Make" dataDxfId="33"/>
+    <tableColumn id="5" name="Duration (Per Dose)" dataDxfId="32"/>
+    <tableColumn id="18" name="Initial Severity" dataDxfId="31"/>
+    <tableColumn id="6" name="Tolerance Gain (Per Dose)" dataDxfId="30"/>
+    <tableColumn id="7" name="Tolerance Fall Rate" dataDxfId="29"/>
+    <tableColumn id="9" name="Addiction Min Tol" dataDxfId="28"/>
+    <tableColumn id="10" name="OD Chance" dataDxfId="27"/>
+    <tableColumn id="11" name="OD Offset" dataDxfId="26"/>
+    <tableColumn id="19" name="Drug Class" dataDxfId="25"/>
+    <tableColumn id="16" name="Type" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table132" displayName="Table132" ref="B3:Q41" totalsRowShown="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table132" displayName="Table132" ref="B3:Q41" totalsRowShown="0" dataDxfId="16">
   <autoFilter ref="B3:Q41"/>
+  <sortState ref="B4:Q41">
+    <sortCondition ref="B3:B41"/>
+  </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" name="Drug" dataDxfId="26"/>
-    <tableColumn id="14" name="Mood Bonus" dataDxfId="25"/>
-    <tableColumn id="13" name="Other Drug Effects" dataDxfId="24"/>
-    <tableColumn id="17" name="Joy" dataDxfId="23"/>
-    <tableColumn id="2" name="Addictiveness" dataDxfId="22"/>
-    <tableColumn id="3" name="Market Value" dataDxfId="21"/>
-    <tableColumn id="4" name="Work to Make" dataDxfId="20"/>
-    <tableColumn id="5" name="Duration (Per Dose)" dataDxfId="19"/>
-    <tableColumn id="18" name="Initial Severity" dataDxfId="18"/>
-    <tableColumn id="6" name="Tolerance Gain (Per Dose)" dataDxfId="17"/>
-    <tableColumn id="7" name="Tolerance Fall Rate" dataDxfId="16"/>
-    <tableColumn id="9" name="Addiction Min Tol" dataDxfId="15"/>
-    <tableColumn id="10" name="OD Chance" dataDxfId="14"/>
-    <tableColumn id="11" name="OD Offset" dataDxfId="13"/>
-    <tableColumn id="19" name="Drug Class" dataDxfId="12"/>
-    <tableColumn id="16" name="Type" dataDxfId="11"/>
+    <tableColumn id="1" name="Drug" dataDxfId="15"/>
+    <tableColumn id="14" name="Mood Bonus" dataDxfId="14"/>
+    <tableColumn id="13" name="Other Drug Effects" dataDxfId="13"/>
+    <tableColumn id="17" name="Joy" dataDxfId="12"/>
+    <tableColumn id="2" name="Addictiveness" dataDxfId="11"/>
+    <tableColumn id="3" name="Market Value" dataDxfId="10"/>
+    <tableColumn id="4" name="Work to Make" dataDxfId="9"/>
+    <tableColumn id="5" name="Duration (Per Dose)" dataDxfId="8"/>
+    <tableColumn id="18" name="Initial Severity" dataDxfId="7"/>
+    <tableColumn id="6" name="Tolerance Gain (Per Dose)" dataDxfId="6"/>
+    <tableColumn id="7" name="Tolerance Fall Rate" dataDxfId="5"/>
+    <tableColumn id="9" name="Addiction Min Tol" dataDxfId="4"/>
+    <tableColumn id="10" name="OD Chance" dataDxfId="3"/>
+    <tableColumn id="11" name="OD Offset" dataDxfId="2"/>
+    <tableColumn id="19" name="Drug Class" dataDxfId="1"/>
+    <tableColumn id="16" name="Type" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1622,154 +1556,154 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:17">
+    <row r="4" spans="2:17" ht="60">
       <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" s="2" customFormat="1">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <v>13</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H5" s="2">
         <v>600</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J5" s="8">
         <v>1</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="5">
-        <v>0</v>
-      </c>
-      <c r="O4" s="6" t="s">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q4" s="6" t="s">
+      <c r="P5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:17" s="2" customFormat="1" ht="90">
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="F5" s="5">
+    <row r="6" spans="2:17">
+      <c r="B6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G5" s="2">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1600</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="L5" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="75">
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.02</v>
-      </c>
       <c r="G6" s="2">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="J6" s="8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L6" s="7">
-        <v>1.4999999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="M6" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N6" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -1874,99 +1808,99 @@
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="2">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2">
-        <v>2000</v>
+        <v>750</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>80</v>
       </c>
       <c r="J9" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>11</v>
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0</v>
       </c>
       <c r="N9" s="5">
         <v>0</v>
       </c>
-      <c r="O9" s="6">
-        <v>0</v>
+      <c r="O9" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:17">
+    <row r="10" spans="2:17" ht="60">
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>91</v>
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F10" s="5">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="2">
-        <v>10</v>
-      </c>
-      <c r="H10" s="2">
-        <v>750</v>
+        <v>43</v>
+      </c>
+      <c r="H10" s="6">
+        <v>400</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J10" s="8">
         <v>0.75</v>
       </c>
       <c r="K10" s="5">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="L10" s="7">
-        <v>0.04</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="M10" s="7">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>13</v>
@@ -2124,63 +2058,63 @@
     </row>
     <row r="14" spans="2:17" ht="75">
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="5">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G14" s="2">
-        <v>88</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1000</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J14" s="8">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>11</v>
+        <v>0.05</v>
+      </c>
+      <c r="L14" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M14" s="7">
+        <v>0.06</v>
       </c>
       <c r="N14" s="5">
-        <v>0</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" ht="105">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>121</v>
+      <c r="D15" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -2189,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="2">
-        <v>95</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>67</v>
+        <v>14</v>
+      </c>
+      <c r="H15" s="6">
+        <v>600</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J15" s="8">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K15" s="5">
         <v>0</v>
@@ -2224,13 +2158,13 @@
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -2239,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="G16" s="2">
-        <v>64</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>67</v>
+        <v>19</v>
+      </c>
+      <c r="H16" s="6">
+        <v>600</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="J16" s="8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -2272,15 +2206,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:17" ht="30">
+    <row r="17" spans="2:17" ht="75">
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -2289,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>67</v>
@@ -2297,7 +2231,7 @@
       <c r="I17" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="8">
         <v>0.33</v>
       </c>
       <c r="K17" s="5">
@@ -2322,65 +2256,65 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:17" ht="75">
+    <row r="18" spans="2:17" ht="105">
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G18" s="2">
-        <v>79</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>67</v>
+        <v>43</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1200</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J18" s="8">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K18" s="5">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>11</v>
+        <v>0.08</v>
+      </c>
+      <c r="L18" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
       </c>
       <c r="N18" s="5">
-        <v>0</v>
-      </c>
-      <c r="O18" s="6">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -2389,13 +2323,13 @@
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H19" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="J19" s="8">
         <v>1</v>
@@ -2422,151 +2356,151 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:17">
+    <row r="20" spans="2:17" ht="45">
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>94</v>
+        <v>12</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="G20" s="2">
+        <v>21</v>
+      </c>
+      <c r="H20" s="6">
+        <v>800</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="N20" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="H20" s="6">
-        <v>600</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="J20" s="8">
-        <v>1</v>
-      </c>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N20" s="5">
-        <v>0</v>
-      </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:17" ht="105">
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="E21" s="4">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="F21" s="5">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G21" s="2">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H21" s="6">
         <v>1200</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J21" s="8">
         <v>0.75</v>
       </c>
       <c r="K21" s="5">
-        <v>0.08</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="L21" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="M21" s="7">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N21" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:17" ht="60">
+    <row r="22" spans="2:17" ht="105">
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="E22" s="4">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2">
-        <v>43</v>
-      </c>
-      <c r="H22" s="6">
-        <v>400</v>
+        <v>95</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="J22" s="8">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="K22" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="L22" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M22" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N22" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
+        <v>0</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>13</v>
@@ -2574,225 +2508,225 @@
     </row>
     <row r="23" spans="2:17">
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E23" s="4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2">
-        <v>6</v>
-      </c>
-      <c r="H23" s="6">
-        <v>350</v>
+        <v>64</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="J23" s="8">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="K23" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="L23" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M23" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N23" s="5">
-        <v>1E-3</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>73</v>
+        <v>0</v>
+      </c>
+      <c r="O23" s="6">
+        <v>0</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="75">
-      <c r="B24" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="2">
-        <v>5</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G24" s="2">
-        <v>35</v>
-      </c>
-      <c r="H24" s="6">
-        <v>350</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="K24" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="L24" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M24" s="7">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q24" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" ht="60">
+    <row r="24" spans="2:17" ht="45">
+      <c r="B24" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>60</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="J24" s="21">
+        <v>1</v>
+      </c>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N24" s="12">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
+      <c r="P24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" ht="30">
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E25" s="4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2">
-        <v>21</v>
-      </c>
-      <c r="H25" s="6">
-        <v>350</v>
+        <v>55</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="8">
-        <v>0.75</v>
+        <v>80</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0.33</v>
       </c>
       <c r="K25" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="L25" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M25" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N25" s="5">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>74</v>
+        <v>0</v>
+      </c>
+      <c r="O25" s="6">
+        <v>0</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="2:17" ht="60">
+    <row r="26" spans="2:17" ht="75">
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E26" s="4">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
-        <v>37</v>
-      </c>
-      <c r="H26" s="6">
-        <v>400</v>
+        <v>79</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="J26" s="8">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K26" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="L26" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M26" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N26" s="5">
-        <v>1.2E-2</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="O26" s="6">
+        <v>0</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>12</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>107</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="E27" s="4">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F27" s="5">
-        <v>7.4999999999999997E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G27" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H27" s="6">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>26</v>
@@ -2801,172 +2735,172 @@
         <v>0.75</v>
       </c>
       <c r="K27" s="5">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="L27" s="7">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="M27" s="7">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N27" s="5">
-        <v>5.0000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" ht="75">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2">
-        <v>20</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>108</v>
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="E28" s="4">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F28" s="5">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H28" s="6">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J28" s="8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K28" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="L28" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M28" s="7">
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N28" s="5">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>75</v>
+        <v>0</v>
+      </c>
+      <c r="O28" s="6">
+        <v>0</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" ht="105">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
       <c r="B29" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C29" s="2">
-        <v>35</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>0</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="4">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="F29" s="5">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="H29" s="6">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J29" s="8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K29" s="5">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="L29" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M29" s="7">
-        <v>0.06</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N29" s="5">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="O29" s="6">
+        <v>0</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="2:17">
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
       </c>
       <c r="F30" s="5">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G30" s="2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H30" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="J30" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K30" s="5">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>11</v>
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="M30" s="7">
+        <v>0.05</v>
       </c>
       <c r="N30" s="5">
         <v>0</v>
       </c>
-      <c r="O30" s="6">
-        <v>0</v>
+      <c r="O30" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="Q30" s="6" t="s">
         <v>13</v>
@@ -2974,13 +2908,13 @@
     </row>
     <row r="31" spans="2:17">
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -2989,13 +2923,13 @@
         <v>0</v>
       </c>
       <c r="G31" s="2">
-        <v>9</v>
-      </c>
-      <c r="H31" s="6">
-        <v>400</v>
+        <v>43</v>
+      </c>
+      <c r="H31" s="2">
+        <v>2000</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="J31" s="8">
         <v>1</v>
@@ -3024,31 +2958,31 @@
     </row>
     <row r="32" spans="2:17">
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C32" s="2">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F32" s="5">
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>13</v>
-      </c>
-      <c r="H32" s="6">
-        <v>600</v>
+        <v>2</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J32" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
@@ -3069,107 +3003,107 @@
         <v>11</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" ht="75">
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>98</v>
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F33" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="G33" s="2">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H33" s="6">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="J33" s="8">
         <v>0.75</v>
       </c>
       <c r="K33" s="5">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="L33" s="7">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="M33" s="7">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N33" s="5">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" ht="60">
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2">
-        <v>12</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>110</v>
+        <v>10</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="E34" s="4">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F34" s="5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G34" s="2">
-        <v>2</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>69</v>
+        <v>21</v>
+      </c>
+      <c r="H34" s="6">
+        <v>350</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J34" s="8">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K34" s="5">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>11</v>
+        <v>0.04</v>
+      </c>
+      <c r="L34" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M34" s="7">
+        <v>0</v>
       </c>
       <c r="N34" s="5">
-        <v>0</v>
-      </c>
-      <c r="O34" s="6">
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="2:17">
@@ -3222,36 +3156,36 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="2:17" ht="60">
+    <row r="36" spans="2:17" ht="90">
       <c r="B36" s="2" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C36" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="E36" s="4">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="F36" s="5">
-        <v>1.2999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G36" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H36" s="2">
         <v>1600</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="J36" s="8">
         <v>0.75</v>
       </c>
       <c r="K36" s="5">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="L36" s="7">
         <v>1.4999999999999999E-2</v>
@@ -3260,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="N36" s="5">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>19</v>
@@ -3374,49 +3308,49 @@
     </row>
     <row r="39" spans="2:17">
       <c r="B39" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
       </c>
       <c r="F39" s="5">
-        <v>0</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G39" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H39" s="2">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J39" s="8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K39" s="5">
-        <v>0</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N39" s="13">
-        <v>7.5000000000000002E-4</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>10</v>
+        <v>0.04</v>
+      </c>
+      <c r="L39" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="M39" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="N39" s="5">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6">
+        <v>0</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>13</v>
@@ -3424,102 +3358,102 @@
     </row>
     <row r="40" spans="2:17">
       <c r="B40" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
       </c>
       <c r="F40" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H40" s="2">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J40" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K40" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="L40" s="7">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="M40" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="N40" s="5">
-        <v>0</v>
-      </c>
-      <c r="O40" s="6">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N40" s="13">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="Q40" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" ht="60">
       <c r="B41" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>116</v>
+        <v>30</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F41" s="5">
-        <v>2.1999999999999999E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G41" s="2">
-        <v>11</v>
-      </c>
-      <c r="H41" s="2">
-        <v>600</v>
+        <v>37</v>
+      </c>
+      <c r="H41" s="6">
+        <v>400</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J41" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K41" s="5">
         <v>0.04</v>
       </c>
       <c r="L41" s="7">
-        <v>4.4999999999999998E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="M41" s="7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="5">
-        <v>0</v>
-      </c>
-      <c r="O41" s="6">
-        <v>0</v>
+        <v>1.2E-2</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="2:17">
@@ -3572,54 +3506,54 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="2:17" ht="45">
-      <c r="B43" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" s="12">
-        <v>0</v>
-      </c>
-      <c r="G43" s="9">
-        <v>60</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I43" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43" s="21">
-        <v>1</v>
-      </c>
-      <c r="K43" s="12">
-        <v>0</v>
-      </c>
-      <c r="L43" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="M43" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="N43" s="12">
-        <v>0</v>
-      </c>
-      <c r="O43" s="10">
-        <v>0</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q43" s="10" t="s">
-        <v>89</v>
+    <row r="43" spans="2:17" ht="75">
+      <c r="B43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="2">
+        <v>35</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F43" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G43" s="2">
+        <v>38</v>
+      </c>
+      <c r="H43" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="L43" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="2:17">
@@ -3786,31 +3720,31 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C44">
-    <cfRule type="cellIs" dxfId="58" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E44">
-    <cfRule type="cellIs" dxfId="56" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q44">
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>"Social Drug"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
       <formula>"Hard Drug"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
       <formula>"Medical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D44">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"No Other Effects"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3917,113 +3851,113 @@
     </row>
     <row r="4" spans="2:17">
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>132</v>
+      <c r="D4" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
       </c>
       <c r="F4" s="5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G4" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J4" s="8">
         <v>0.75</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>11</v>
+        <v>0.03</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M4" s="7">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="N4" s="5">
         <v>0</v>
       </c>
-      <c r="O4" s="6">
-        <v>0</v>
+      <c r="O4" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>11</v>
+        <v>159</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:17" s="2" customFormat="1">
+    <row r="5" spans="2:17" s="2" customFormat="1" ht="30">
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>130</v>
+        <v>-3</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G5" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J5" s="8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>11</v>
+        <v>0.03</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
+        <v>0.04</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>134</v>
+      <c r="D6" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -4032,34 +3966,34 @@
         <v>0.01</v>
       </c>
       <c r="G6" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="J6" s="8">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="L6" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M6" s="7">
         <v>0.03</v>
       </c>
-      <c r="L6" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M6" s="7">
-        <v>3.5000000000000003E-2</v>
-      </c>
       <c r="N6" s="5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>10</v>
+        <v>142</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q6" s="6" t="s">
         <v>13</v>
@@ -4067,64 +4001,64 @@
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C7" s="2">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6">
+        <v>400</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="B8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="G7" s="2">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2">
-        <v>700</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="L7" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0.08</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="30">
-      <c r="B8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="E8" s="4">
         <v>0</v>
       </c>
@@ -4132,75 +4066,57 @@
         <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>16</v>
-      </c>
-      <c r="H8" s="2">
-        <v>500</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" s="8">
-        <v>1</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N8" s="5">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
       <c r="Q8" s="6" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="2" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G9" s="2">
-        <v>120</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>67</v>
+        <v>24</v>
+      </c>
+      <c r="H9" s="2">
+        <v>700</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="J9" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>11</v>
+        <v>0.05</v>
+      </c>
+      <c r="L9" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0.08</v>
       </c>
       <c r="N9" s="5">
         <v>0</v>
@@ -4209,74 +4125,74 @@
         <v>0</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="2" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="C10" s="2">
-        <v>24</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>111</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="E10" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>35</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1000</v>
+        <v>28</v>
+      </c>
+      <c r="H10" s="6">
+        <v>750</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J10" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K10" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="L10" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N10" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>137</v>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>141</v>
+        <v>24</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F11" s="5">
         <v>0.02</v>
@@ -4291,10 +4207,10 @@
         <v>135</v>
       </c>
       <c r="J11" s="8">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L11" s="7">
         <v>1.4999999999999999E-2</v>
@@ -4303,10 +4219,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>143</v>
@@ -4315,115 +4231,115 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="30">
+    <row r="12" spans="2:17">
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="C12" s="2">
-        <v>-3</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>160</v>
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
       </c>
       <c r="F12" s="5">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J12" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K12" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="L12" s="7">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N12" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>144</v>
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>150</v>
+      <c r="D13" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G13" s="2">
-        <v>16</v>
-      </c>
-      <c r="H13" s="6">
-        <v>400</v>
+        <v>35</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1000</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="J13" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>11</v>
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="M13" s="7">
+        <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>0</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="2" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>148</v>
+      <c r="D14" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
@@ -4432,16 +4348,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <v>28</v>
-      </c>
-      <c r="H14" s="6">
-        <v>750</v>
+        <v>22</v>
+      </c>
+      <c r="H14" s="2">
+        <v>600</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="J14" s="8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K14" s="5">
         <v>0</v>
@@ -4467,63 +4383,63 @@
     </row>
     <row r="15" spans="2:17">
       <c r="B15" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
       </c>
       <c r="F15" s="5">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
-        <v>25</v>
-      </c>
-      <c r="H15" s="2">
-        <v>800</v>
+        <v>120</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="J15" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K15" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="L15" s="7">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="M15" s="7">
-        <v>0.03</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="N15" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>142</v>
+        <v>0</v>
+      </c>
+      <c r="O15" s="6">
+        <v>0</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:17">
+    <row r="16" spans="2:17" ht="30">
       <c r="B16" s="2" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>90</v>
+      <c r="D16" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -4532,19 +4448,37 @@
         <v>0</v>
       </c>
       <c r="G16" s="2">
-        <v>10</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="H16" s="2">
+        <v>500</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="Q16" s="6" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:17">
@@ -5179,31 +5113,31 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C41">
-    <cfRule type="cellIs" dxfId="34" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E41">
-    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q41">
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
       <formula>"Social Drug"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
       <formula>"Hard Drug"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>"Medical"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:D41 D4:D8">
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>"No Other Effects"</formula>
     </cfRule>
   </conditionalFormatting>
